--- a/sample/国际表单独称重示例.xlsx
+++ b/sample/国际表单独称重示例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RenSheet\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1728983-FAD7-4491-8DBA-AF3173EA0D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95F89CD-FE00-44C0-82B0-7CB9F90777AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,15 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>cn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本体（克）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>张三</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -388,28 +380,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+      <c r="B1" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>200</v>
@@ -417,41 +409,33 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
         <v>300</v>
       </c>
     </row>
